--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -1845,22 +1845,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>U.N.A.M.</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M25" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>13</v>
+      </c>
+      <c r="O25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -1903,22 +1903,62 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M26" t="n">
+        <v>17</v>
+      </c>
+      <c r="N26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -1961,40 +1961,120 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M27" t="n">
+        <v>16</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08/03/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tigres</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>13</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -2077,22 +2077,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Juarez</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>24</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -2135,22 +2135,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M30" t="n">
+        <v>22</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -2193,22 +2193,62 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Atl. San Luis</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>15</v>
+      </c>
+      <c r="O31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -2251,22 +2251,62 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M32" t="n">
+        <v>17</v>
+      </c>
+      <c r="N32" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -2309,22 +2309,62 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M33" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9</v>
+      </c>
+      <c r="O33" t="n">
+        <v>6</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -2367,40 +2367,120 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M34" t="n">
+        <v>23</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>6</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Santos Laguna</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M35" t="n">
+        <v>16</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -511,22 +511,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Santos Laguna</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" t="n">
+        <v>13</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -569,22 +569,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -627,22 +627,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>

--- a/new-stats/cf-monterrey.xlsx
+++ b/new-stats/cf-monterrey.xlsx
@@ -685,22 +685,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Juarez</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
